--- a/demos/03_excel_report/output/매출_통합보고서.xlsx
+++ b/demos/03_excel_report/output/매출_통합보고서.xlsx
@@ -852,7 +852,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>자동 생성 2026-10-29 22:42 · 원본 5개 파일 · 지점 5곳</t>
+          <t>자동 생성 2026-10-30 01:21 · 원본 5개 파일 · 지점 5곳</t>
         </is>
       </c>
     </row>
